--- a/tests/perf_v2/perf_history/v2.5/detection/DETECTION-raw-bdd_medium.xlsx
+++ b/tests/perf_v2/perf_history/v2.5/detection/DETECTION-raw-bdd_medium.xlsx
@@ -7,15 +7,15 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="atss_mobilenetv2" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="atss_resnext101" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dfine_x" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtdetr_101" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtdetr_18" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtdetr_50" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtmdet_tiny" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ssd_mobilenetv2" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yolox_l" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="atss_resnext101" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dfine_x" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtdetr_101" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtdetr_18" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtdetr_50" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ssd_mobilenetv2" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yolox_l" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="atss_mobilenetv2" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtmdet_tiny" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yolox_s" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yolox_tiny" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yolox_x" sheetId="12" state="visible" r:id="rId12"/>
@@ -596,56 +596,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>448.6250975131989</v>
+        <v>687.0883150100708</v>
       </c>
       <c r="D2" t="n">
-        <v>6.96999979019165</v>
+        <v>15.39999961853027</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1936255525458942</v>
+        <v>0.5250663757324219</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5659946799278259</v>
+        <v>0.6046698689460754</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5367303490638733</v>
+        <v>0.5639751553535461</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5369458198547363</v>
+        <v>0.5601750612258911</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5387062430381775</v>
+        <v>0.5555555820465088</v>
       </c>
       <c r="J2" t="n">
-        <v>0.101590871810913</v>
+        <v>0.1793572604656219</v>
       </c>
       <c r="K2" t="n">
-        <v>81.03700661659241</v>
+        <v>516.870762348175</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0413314421971639</v>
+        <v>0.07532960891723629</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0576924975713094</v>
+        <v>0.4339489920934041</v>
       </c>
       <c r="N2" t="n">
-        <v>0.055047378540039</v>
+        <v>0.1330336793263753</v>
       </c>
       <c r="O2" t="n">
-        <v>6.199716329574585</v>
+        <v>11.29944133758545</v>
       </c>
       <c r="P2" t="n">
-        <v>8.653874635696411</v>
+        <v>65.09234881401062</v>
       </c>
       <c r="Q2" t="n">
-        <v>8.257106781005859</v>
+        <v>19.9550518989563</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250627-172835</t>
+          <t>20250726-031747</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -655,7 +655,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>atss_mobilenetv2</t>
+          <t>atss_resnext101</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -670,22 +670,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -717,56 +717,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="C3" t="n">
-        <v>338.2517077922821</v>
+        <v>1052.358206033707</v>
       </c>
       <c r="D3" t="n">
-        <v>6.71999979019165</v>
+        <v>15.4399995803833</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1935463482286871</v>
+        <v>0.5268095326423645</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5704028606414795</v>
+        <v>0.6202875971794128</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5346410870552063</v>
+        <v>0.5709536671638489</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5355722308158875</v>
+        <v>0.5681222677230835</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5385469794273376</v>
+        <v>0.5677474737167358</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1004696562886238</v>
+        <v>0.17993925511837</v>
       </c>
       <c r="K3" t="n">
-        <v>79.39242696762085</v>
+        <v>510.8430435657501</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0392441908518473</v>
+        <v>0.07441059271494541</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0540985774993896</v>
+        <v>0.4391837819417317</v>
       </c>
       <c r="N3" t="n">
-        <v>0.054418404897054</v>
+        <v>0.1330678494771321</v>
       </c>
       <c r="O3" t="n">
-        <v>5.8866286277771</v>
+        <v>11.16158890724182</v>
       </c>
       <c r="P3" t="n">
-        <v>8.114786624908447</v>
+        <v>65.87756729125977</v>
       </c>
       <c r="Q3" t="n">
-        <v>8.162760734558105</v>
+        <v>19.96017742156982</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250627-173818</t>
+          <t>20250726-034009</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>atss_mobilenetv2</t>
+          <t>atss_resnext101</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -791,22 +791,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -838,56 +838,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C4" t="n">
-        <v>211.3316407203674</v>
+        <v>975.0596017837524</v>
       </c>
       <c r="D4" t="n">
-        <v>6.710000038146973</v>
+        <v>15.39999961853027</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1946363520622253</v>
+        <v>0.5292992799178414</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5670216679573059</v>
+        <v>0.6186937689781189</v>
       </c>
       <c r="G4" t="n">
-        <v>0.536729097366333</v>
+        <v>0.5719519853591919</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5373949408531189</v>
+        <v>0.5718361735343933</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5356004238128662</v>
+        <v>0.5779109597206116</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0968440026044845</v>
+        <v>0.1792986989021301</v>
       </c>
       <c r="K4" t="n">
-        <v>81.23124194145203</v>
+        <v>509.2813761234283</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0387825568517049</v>
+        <v>0.0747277545928955</v>
       </c>
       <c r="M4" t="n">
-        <v>0.055232655207316</v>
+        <v>0.4405744377772013</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0552035125096639</v>
+        <v>0.1345976734161377</v>
       </c>
       <c r="O4" t="n">
-        <v>5.817383527755737</v>
+        <v>11.20916318893433</v>
       </c>
       <c r="P4" t="n">
-        <v>8.284898281097412</v>
+        <v>66.0861656665802</v>
       </c>
       <c r="Q4" t="n">
-        <v>8.280526876449585</v>
+        <v>20.18965101242065</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250627-174620</t>
+          <t>20250726-040831</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>atss_mobilenetv2</t>
+          <t>atss_resnext101</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -912,22 +912,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -959,56 +959,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C5" t="n">
-        <v>273.1337945461273</v>
+        <v>1130.769727230072</v>
       </c>
       <c r="D5" t="n">
-        <v>6.71999979019165</v>
+        <v>15.39999961853027</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1931538392197001</v>
+        <v>0.5283713892654136</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5707565546035767</v>
+        <v>0.6177884340286255</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5261584520339966</v>
+        <v>0.5853658318519592</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5249679684638977</v>
+        <v>0.5794143676757812</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5229259729385376</v>
+        <v>0.5837405323982239</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0980679020285606</v>
+        <v>0.1797197461128235</v>
       </c>
       <c r="K5" t="n">
-        <v>79.88996696472168</v>
+        <v>507.5915777683258</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0382463757197062</v>
+        <v>0.07467003822326659</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0542384513219197</v>
+        <v>0.4375485610961914</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0522336626052856</v>
+        <v>0.1328072166442871</v>
       </c>
       <c r="O5" t="n">
-        <v>5.736956357955933</v>
+        <v>11.20050573348999</v>
       </c>
       <c r="P5" t="n">
-        <v>8.135767698287964</v>
+        <v>65.63228416442871</v>
       </c>
       <c r="Q5" t="n">
-        <v>7.835049390792847</v>
+        <v>19.92108249664306</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250627-175217</t>
+          <t>20250726-043535</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>atss_mobilenetv2</t>
+          <t>atss_resnext101</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1033,22 +1033,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1080,56 +1080,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="C6" t="n">
-        <v>289.305410861969</v>
+        <v>1129.302535533905</v>
       </c>
       <c r="D6" t="n">
-        <v>6.96999979019165</v>
+        <v>15.39999961853027</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1930527384792054</v>
+        <v>0.5278112270213939</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5642105340957642</v>
+        <v>0.6195696592330933</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5289501547813416</v>
+        <v>0.5759637355804443</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5277777910232544</v>
+        <v>0.5795009136199951</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5268358588218689</v>
+        <v>0.5777106881141663</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0949276313185691</v>
+        <v>0.1796835958957672</v>
       </c>
       <c r="K6" t="n">
-        <v>80.33323335647583</v>
+        <v>511.5842018127441</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0387941757837931</v>
+        <v>0.076962718963623</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0570641485850016</v>
+        <v>0.4476278893152873</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0534342877070109</v>
+        <v>0.1339571873346964</v>
       </c>
       <c r="O6" t="n">
-        <v>5.81912636756897</v>
+        <v>11.54440784454346</v>
       </c>
       <c r="P6" t="n">
-        <v>8.559622287750244</v>
+        <v>67.14418339729309</v>
       </c>
       <c r="Q6" t="n">
-        <v>8.015143156051636</v>
+        <v>20.09357810020447</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250627-175913</t>
+          <t>20250726-050521</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>atss_mobilenetv2</t>
+          <t>atss_resnext101</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1154,22 +1154,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -3680,56 +3680,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="C2" t="n">
-        <v>485.6145024299622</v>
+        <v>919.2638807296752</v>
       </c>
       <c r="D2" t="n">
-        <v>9.720000267028809</v>
+        <v>20.42000007629395</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3172159142353955</v>
+        <v>0.6021269252805999</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6105844974517822</v>
+        <v>0.6808176040649414</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5595990419387817</v>
+        <v>0.6327908039093018</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5594771504402161</v>
+        <v>0.6338373422622681</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5623770952224731</v>
+        <v>0.500349760055542</v>
       </c>
       <c r="J2" t="n">
-        <v>0.133255586028099</v>
+        <v>0.135452315211296</v>
       </c>
       <c r="K2" t="n">
-        <v>510.7270305156708</v>
+        <v>889.6361842155457</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0715093819300333</v>
+        <v>0.07235104719797771</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4450257078806559</v>
+        <v>0.1707724539438883</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1339868958791097</v>
+        <v>0.1130779202779134</v>
       </c>
       <c r="O2" t="n">
-        <v>10.726407289505</v>
+        <v>10.85265707969666</v>
       </c>
       <c r="P2" t="n">
-        <v>66.75385618209839</v>
+        <v>25.61586809158325</v>
       </c>
       <c r="Q2" t="n">
-        <v>20.09803438186645</v>
+        <v>16.96168804168701</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250629-100017</t>
+          <t>20250724-233249</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>atss_resnext101</t>
+          <t>dfine_x</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -3754,22 +3754,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -3804,53 +3804,53 @@
         <v>21</v>
       </c>
       <c r="C3" t="n">
-        <v>596.04949259758</v>
+        <v>596.2973520755768</v>
       </c>
       <c r="D3" t="n">
-        <v>9.789999961853027</v>
+        <v>20.42000007629395</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3230645571436201</v>
+        <v>0.5996452484812055</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6220383644104004</v>
+        <v>0.6671565175056458</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5662882924079895</v>
+        <v>0.6335204243659973</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5642014741897583</v>
+        <v>0.6329219937324524</v>
       </c>
       <c r="I3" t="n">
-        <v>0.564091682434082</v>
+        <v>0.633243203163147</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1307968497276306</v>
+        <v>0.1328088939189911</v>
       </c>
       <c r="K3" t="n">
-        <v>535.8759219646454</v>
+        <v>881.3348248004913</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0732484038670857</v>
+        <v>0.0730671612421671</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4423090442021687</v>
+        <v>0.1692089128494262</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1346043809254964</v>
+        <v>0.1143027512232462</v>
       </c>
       <c r="O3" t="n">
-        <v>10.98726058006287</v>
+        <v>10.96007418632507</v>
       </c>
       <c r="P3" t="n">
-        <v>66.34635663032532</v>
+        <v>25.38133692741394</v>
       </c>
       <c r="Q3" t="n">
-        <v>20.19065713882446</v>
+        <v>17.14541268348694</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250629-101914</t>
+          <t>20250725-000450</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>atss_resnext101</t>
+          <t>dfine_x</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -3875,22 +3875,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -3922,56 +3922,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="C4" t="n">
-        <v>508.9376575946808</v>
+        <v>808.8499670028687</v>
       </c>
       <c r="D4" t="n">
-        <v>9.720000267028809</v>
+        <v>21.01000022888184</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3152066999011569</v>
+        <v>0.6002512224789324</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6121476888656616</v>
+        <v>0.6797880530357361</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5761094689369202</v>
+        <v>0.6336475014686584</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5643453001976013</v>
+        <v>0.6287263035774231</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5613239407539368</v>
+        <v>0.6257591843605042</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1340768933296203</v>
+        <v>0.1570975929498672</v>
       </c>
       <c r="K4" t="n">
-        <v>516.2488777637482</v>
+        <v>881.3526802062988</v>
       </c>
       <c r="L4" t="n">
-        <v>0.07249103387196849</v>
+        <v>0.07400222937266029</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4355597654978434</v>
+        <v>0.1670270331700643</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1349215237299601</v>
+        <v>0.1136019261678059</v>
       </c>
       <c r="O4" t="n">
-        <v>10.87365508079529</v>
+        <v>11.10033440589905</v>
       </c>
       <c r="P4" t="n">
-        <v>65.33396482467651</v>
+        <v>25.05405497550964</v>
       </c>
       <c r="Q4" t="n">
-        <v>20.23822855949402</v>
+        <v>17.0402889251709</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250629-104027</t>
+          <t>20250725-003120</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>atss_resnext101</t>
+          <t>dfine_x</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -3996,22 +3996,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -4043,56 +4043,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C5" t="n">
-        <v>532.6605257987976</v>
+        <v>703.8756294250488</v>
       </c>
       <c r="D5" t="n">
-        <v>9.75</v>
+        <v>20.3799991607666</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3136947986326719</v>
+        <v>0.6038006567955017</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6097201704978943</v>
+        <v>0.6756237745285034</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5594713687896729</v>
+        <v>0.6249240040779114</v>
       </c>
       <c r="H5" t="n">
-        <v>0.559542179107666</v>
+        <v>0.6182048320770264</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5620530247688293</v>
+        <v>0.6162024140357971</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1308030933141708</v>
+        <v>0.1364432722330093</v>
       </c>
       <c r="K5" t="n">
-        <v>512.5853679180145</v>
+        <v>887.7688300609589</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0694947338104248</v>
+        <v>0.0719228506088256</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4384239387512207</v>
+        <v>0.1654714107513427</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1312241458892822</v>
+        <v>0.1116120735804239</v>
       </c>
       <c r="O5" t="n">
-        <v>10.42421007156372</v>
+        <v>10.78842759132385</v>
       </c>
       <c r="P5" t="n">
-        <v>65.76359081268311</v>
+        <v>24.82071161270142</v>
       </c>
       <c r="Q5" t="n">
-        <v>19.68362188339233</v>
+        <v>16.7418110370636</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250629-105951</t>
+          <t>20250725-010132</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>atss_resnext101</t>
+          <t>dfine_x</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -4117,22 +4117,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -4164,56 +4164,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C6" t="n">
-        <v>655.0322272777557</v>
+        <v>485.3209960460663</v>
       </c>
       <c r="D6" t="n">
-        <v>9.789999961853027</v>
+        <v>22.38999938964844</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3217890586542046</v>
+        <v>0.5989271437420565</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6145374178886414</v>
+        <v>0.6860643029212952</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5823754668235779</v>
+        <v>0.6190745830535889</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5789697766304016</v>
+        <v>0.6090739369392395</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5805354714393616</v>
+        <v>0.6100993156433105</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1333580911159515</v>
+        <v>0.1339640021324157</v>
       </c>
       <c r="K6" t="n">
-        <v>520.8531577587128</v>
+        <v>922.1913812160492</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0693325535456339</v>
+        <v>0.0722785854339599</v>
       </c>
       <c r="M6" t="n">
-        <v>0.439444416364034</v>
+        <v>0.1659322913487752</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1341458145777384</v>
+        <v>0.1123688570658365</v>
       </c>
       <c r="O6" t="n">
-        <v>10.39988303184509</v>
+        <v>10.84178781509399</v>
       </c>
       <c r="P6" t="n">
-        <v>65.9166624546051</v>
+        <v>24.88984370231628</v>
       </c>
       <c r="Q6" t="n">
-        <v>20.12187218666077</v>
+        <v>16.85532855987549</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250629-111935</t>
+          <t>20250725-012954</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>atss_resnext101</t>
+          <t>dfine_x</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -4238,22 +4238,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -4451,56 +4451,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="C2" t="n">
-        <v>473.4492180347443</v>
+        <v>948.3739910125732</v>
       </c>
       <c r="D2" t="n">
-        <v>14.28999996185303</v>
+        <v>11.15999984741211</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5249899261527591</v>
+        <v>0.3267080523073673</v>
       </c>
       <c r="F2" t="n">
-        <v>0.656410276889801</v>
+        <v>0.6654288768768311</v>
       </c>
       <c r="G2" t="n">
-        <v>0.619963526725769</v>
+        <v>0.6433305740356445</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6179751753807068</v>
+        <v>0.6372023224830627</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6198259592056274</v>
+        <v>0.6307196617126465</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1264929622411728</v>
+        <v>0.148377776145935</v>
       </c>
       <c r="K2" t="n">
-        <v>893.5126669406891</v>
+        <v>241.8114793300629</v>
       </c>
       <c r="L2" t="n">
-        <v>0.07210392634073889</v>
+        <v>0.07833818912506101</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1655577691396077</v>
+        <v>0.1971492354075114</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1138079341252644</v>
+        <v>0.1206238635381062</v>
       </c>
       <c r="O2" t="n">
-        <v>10.81558895111084</v>
+        <v>11.75072836875916</v>
       </c>
       <c r="P2" t="n">
-        <v>24.83366537094116</v>
+        <v>29.57238531112671</v>
       </c>
       <c r="Q2" t="n">
-        <v>17.07119011878967</v>
+        <v>18.09357953071594</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250628-183639</t>
+          <t>20250727-091754</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>dfine_x</t>
+          <t>rtdetr_101</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -4525,22 +4525,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -4572,56 +4572,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="C3" t="n">
-        <v>422.1894478797913</v>
+        <v>836.2760767936707</v>
       </c>
       <c r="D3" t="n">
-        <v>14.68000030517578</v>
+        <v>10.88000011444092</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5237028039991856</v>
+        <v>0.3259420011724744</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6640625</v>
+        <v>0.6702371835708618</v>
       </c>
       <c r="G3" t="n">
-        <v>0.609967052936554</v>
+        <v>0.6516270637512207</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6021322011947632</v>
+        <v>0.6521739363670349</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6008602380752563</v>
+        <v>0.6493295431137085</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1249769181013107</v>
+        <v>0.1704914569854736</v>
       </c>
       <c r="K3" t="n">
-        <v>898.4529454708099</v>
+        <v>241.2440330982209</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07227610905965159</v>
+        <v>0.0796181042989095</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1667233324050903</v>
+        <v>0.2001260741551717</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1135259548823038</v>
+        <v>0.1181208499272664</v>
       </c>
       <c r="O3" t="n">
-        <v>10.84141635894775</v>
+        <v>11.94271564483643</v>
       </c>
       <c r="P3" t="n">
-        <v>25.00849986076355</v>
+        <v>30.01891112327576</v>
       </c>
       <c r="Q3" t="n">
-        <v>17.02889323234558</v>
+        <v>17.71812748908997</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250628-190117</t>
+          <t>20250727-093948</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>dfine_x</t>
+          <t>rtdetr_101</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -4646,22 +4646,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -4693,56 +4693,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="C4" t="n">
-        <v>429.5663719177246</v>
+        <v>1002.014010190964</v>
       </c>
       <c r="D4" t="n">
-        <v>14.19999980926514</v>
+        <v>11.42000007629394</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5221000649034977</v>
+        <v>0.3262483416234745</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6666666865348816</v>
+        <v>0.6702702641487122</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6453250050544739</v>
+        <v>0.6434923410415649</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6383246183395386</v>
+        <v>0.6401454210281372</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6330814361572266</v>
+        <v>0.6384100317955017</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1242772936820983</v>
+        <v>0.1466061472892761</v>
       </c>
       <c r="K4" t="n">
-        <v>889.1983275413513</v>
+        <v>238.989592552185</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0751287142435709</v>
+        <v>0.0773210287094116</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1672032213211059</v>
+        <v>0.1965127070744832</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1152153714497884</v>
+        <v>0.1213944864273071</v>
       </c>
       <c r="O4" t="n">
-        <v>11.26930713653564</v>
+        <v>11.59815430641174</v>
       </c>
       <c r="P4" t="n">
-        <v>25.08048319816589</v>
+        <v>29.47690606117249</v>
       </c>
       <c r="Q4" t="n">
-        <v>17.28230571746826</v>
+        <v>18.20917296409607</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250628-192509</t>
+          <t>20250727-095940</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>dfine_x</t>
+          <t>rtdetr_101</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -4767,22 +4767,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -4814,56 +4814,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C5" t="n">
-        <v>428.8153593540192</v>
+        <v>609.4761292934418</v>
       </c>
       <c r="D5" t="n">
-        <v>14.09000015258789</v>
+        <v>10.65999984741211</v>
       </c>
       <c r="E5" t="n">
-        <v>0.52865244820714</v>
+        <v>0.3288690254092216</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6646130084991455</v>
+        <v>0.6527726054191589</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6234897971153259</v>
+        <v>0.6227962374687195</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6216163039207458</v>
+        <v>0.6213671565055847</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6146225333213806</v>
+        <v>0.6120600700378418</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1236042901873588</v>
+        <v>0.145743191242218</v>
       </c>
       <c r="K5" t="n">
-        <v>895.9830591678619</v>
+        <v>233.6324570178986</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07074362277984619</v>
+        <v>0.075626212755839</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1672558307647705</v>
+        <v>0.1969092321395874</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1139234654108683</v>
+        <v>0.1208492136001587</v>
       </c>
       <c r="O5" t="n">
-        <v>10.61154341697693</v>
+        <v>11.34393191337585</v>
       </c>
       <c r="P5" t="n">
-        <v>25.08837461471558</v>
+        <v>29.53638482093811</v>
       </c>
       <c r="Q5" t="n">
-        <v>17.08851981163025</v>
+        <v>18.1273820400238</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250628-194901</t>
+          <t>20250727-102224</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>dfine_x</t>
+          <t>rtdetr_101</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -4888,22 +4888,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -4935,56 +4935,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="C6" t="n">
-        <v>423.6146941184998</v>
+        <v>995.622980117798</v>
       </c>
       <c r="D6" t="n">
-        <v>14.18000030517578</v>
+        <v>11.57999992370606</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5249391086399555</v>
+        <v>0.3251563214203891</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6580022573471069</v>
+        <v>0.6679596304893494</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6098566651344299</v>
+        <v>0.6462793350219727</v>
       </c>
       <c r="H6" t="n">
-        <v>0.608798086643219</v>
+        <v>0.6422781348228455</v>
       </c>
       <c r="I6" t="n">
-        <v>0.602066695690155</v>
+        <v>0.6361936330795288</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1239719539880752</v>
+        <v>0.1484228372573852</v>
       </c>
       <c r="K6" t="n">
-        <v>896.5235040187836</v>
+        <v>237.0508303642273</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0739818938573201</v>
+        <v>0.0768060461680094</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1686812114715576</v>
+        <v>0.1971502272288004</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1150968360900878</v>
+        <v>0.1181130488713582</v>
       </c>
       <c r="O6" t="n">
-        <v>11.09728407859802</v>
+        <v>11.52090692520142</v>
       </c>
       <c r="P6" t="n">
-        <v>25.30218172073364</v>
+        <v>29.57253408432007</v>
       </c>
       <c r="Q6" t="n">
-        <v>17.26452541351318</v>
+        <v>17.71695733070374</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250628-201307</t>
+          <t>20250727-103820</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>dfine_x</t>
+          <t>rtdetr_101</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -5009,22 +5009,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -5222,56 +5222,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C2" t="n">
-        <v>458.0901186466217</v>
+        <v>349.9055676460266</v>
       </c>
       <c r="D2" t="n">
-        <v>9.75</v>
+        <v>5.46999979019165</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2979960683733225</v>
+        <v>0.1596991838443846</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6677128076553345</v>
+        <v>0.6197404861450195</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6467641592025757</v>
+        <v>0.5870746970176697</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6455492973327637</v>
+        <v>0.5889981389045715</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6405722498893738</v>
+        <v>0.5877061486244202</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1264332085847854</v>
+        <v>0.0693811178207397</v>
       </c>
       <c r="K2" t="n">
-        <v>240.6455547809601</v>
+        <v>85.43479919433594</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0773960336049397</v>
+        <v>0.0608450841903686</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1988353411356608</v>
+        <v>0.0690841929117838</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1196424595514933</v>
+        <v>0.0598643811543782</v>
       </c>
       <c r="O2" t="n">
-        <v>11.60940504074097</v>
+        <v>9.126762628555298</v>
       </c>
       <c r="P2" t="n">
-        <v>29.82530117034912</v>
+        <v>10.36262893676758</v>
       </c>
       <c r="Q2" t="n">
-        <v>17.946368932724</v>
+        <v>8.979657173156738</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250630-071012</t>
+          <t>20250728-111634</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>rtdetr_101</t>
+          <t>rtdetr_18</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -5296,22 +5296,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -5343,56 +5343,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="C3" t="n">
-        <v>471.8447201251984</v>
+        <v>573.4838852882385</v>
       </c>
       <c r="D3" t="n">
-        <v>9.899999618530272</v>
+        <v>5.5</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2989278044551611</v>
+        <v>0.1608160529817853</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6553584933280945</v>
+        <v>0.624054491519928</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6312185525894165</v>
+        <v>0.5910496711730957</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6297461986541748</v>
+        <v>0.5908620953559875</v>
       </c>
       <c r="I3" t="n">
-        <v>0.631798267364502</v>
+        <v>0.5789134502410889</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1264070272445678</v>
+        <v>0.0732057467103004</v>
       </c>
       <c r="K3" t="n">
-        <v>238.4576828479767</v>
+        <v>86.70452976226807</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0820717811584472</v>
+        <v>0.0617495965957641</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2008057419459025</v>
+        <v>0.06618752956390379</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1179019196828206</v>
+        <v>0.0600635798772176</v>
       </c>
       <c r="O3" t="n">
-        <v>12.31076717376709</v>
+        <v>9.262439489364624</v>
       </c>
       <c r="P3" t="n">
-        <v>30.12086129188538</v>
+        <v>9.928129434585571</v>
       </c>
       <c r="Q3" t="n">
-        <v>17.6852879524231</v>
+        <v>9.009536981582642</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250630-072345</t>
+          <t>20250728-112453</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>rtdetr_101</t>
+          <t>rtdetr_18</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -5417,22 +5417,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -5464,56 +5464,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="C4" t="n">
-        <v>466.2519690990448</v>
+        <v>592.5501663684845</v>
       </c>
       <c r="D4" t="n">
-        <v>10.39000034332275</v>
+        <v>5.579999923706055</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2995012756437063</v>
+        <v>0.1648439926405747</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6613756418228149</v>
+        <v>0.6161943078041077</v>
       </c>
       <c r="G4" t="n">
-        <v>0.620675802230835</v>
+        <v>0.5877736210823059</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6100208759307861</v>
+        <v>0.5832614302635193</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6178225874900818</v>
+        <v>0.58200603723526</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1256716102361679</v>
+        <v>0.06871532648801799</v>
       </c>
       <c r="K4" t="n">
-        <v>235.7067589759827</v>
+        <v>87.72047567367554</v>
       </c>
       <c r="L4" t="n">
-        <v>0.08083769957224519</v>
+        <v>0.0612219762802124</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1982454888025919</v>
+        <v>0.0690671443939208</v>
       </c>
       <c r="N4" t="n">
-        <v>0.118249397277832</v>
+        <v>0.0593836291631062</v>
       </c>
       <c r="O4" t="n">
-        <v>12.12565493583679</v>
+        <v>9.18329644203186</v>
       </c>
       <c r="P4" t="n">
-        <v>29.7368233203888</v>
+        <v>10.36007165908814</v>
       </c>
       <c r="Q4" t="n">
-        <v>17.7374095916748</v>
+        <v>8.907544374465942</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250630-073730</t>
+          <t>20250728-113717</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>rtdetr_101</t>
+          <t>rtdetr_18</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -5538,22 +5538,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -5585,56 +5585,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C5" t="n">
-        <v>466.6920704841614</v>
+        <v>333.6581492424011</v>
       </c>
       <c r="D5" t="n">
-        <v>9.920000076293944</v>
+        <v>5.5</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3034541737288236</v>
+        <v>0.1613585144281387</v>
       </c>
       <c r="F5" t="n">
-        <v>0.659476101398468</v>
+        <v>0.6225831508636475</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6302288770675659</v>
+        <v>0.5785156488418579</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6138870716094971</v>
+        <v>0.5726214051246643</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6139777898788452</v>
+        <v>0.5666082501411438</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1469757407903671</v>
+        <v>0.0697907507419586</v>
       </c>
       <c r="K5" t="n">
-        <v>256.18949842453</v>
+        <v>86.80782508850098</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08048334439595541</v>
+        <v>0.0615243323644002</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1950280427932739</v>
+        <v>0.0688128026326497</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1183579778671264</v>
+        <v>0.059992135365804</v>
       </c>
       <c r="O5" t="n">
-        <v>12.07250165939331</v>
+        <v>9.228649854660034</v>
       </c>
       <c r="P5" t="n">
-        <v>29.25420641899109</v>
+        <v>10.32192039489746</v>
       </c>
       <c r="Q5" t="n">
-        <v>17.75369668006897</v>
+        <v>8.998820304870605</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250630-075106</t>
+          <t>20250728-114941</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -5644,7 +5644,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>rtdetr_101</t>
+          <t>rtdetr_18</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -5659,22 +5659,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -5706,56 +5706,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="C6" t="n">
-        <v>518.2580780982971</v>
+        <v>476.5130124092102</v>
       </c>
       <c r="D6" t="n">
-        <v>9.729999542236328</v>
+        <v>5.650000095367432</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3021762238608466</v>
+        <v>0.163659972877338</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6512205004692078</v>
+        <v>0.6209900975227356</v>
       </c>
       <c r="G6" t="n">
-        <v>0.594197154045105</v>
+        <v>0.599587619304657</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5963666439056396</v>
+        <v>0.5977768898010254</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5875590443611145</v>
+        <v>0.5781673789024353</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1247311905026435</v>
+        <v>0.0694640278816223</v>
       </c>
       <c r="K6" t="n">
-        <v>266.3326740264893</v>
+        <v>87.11280941963196</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0810859934488932</v>
+        <v>0.0578378582000732</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2009078439076741</v>
+        <v>0.0701984707514445</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1184460608164469</v>
+        <v>0.0593739891052246</v>
       </c>
       <c r="O6" t="n">
-        <v>12.16289901733398</v>
+        <v>8.675678730010986</v>
       </c>
       <c r="P6" t="n">
-        <v>30.13617658615112</v>
+        <v>10.52977061271668</v>
       </c>
       <c r="Q6" t="n">
-        <v>17.76690912246704</v>
+        <v>8.906098365783691</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250630-080503</t>
+          <t>20250728-115746</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>rtdetr_101</t>
+          <t>rtdetr_18</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -5780,22 +5780,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -5993,56 +5993,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C2" t="n">
-        <v>293.9251608848572</v>
+        <v>512.1237831115723</v>
       </c>
       <c r="D2" t="n">
-        <v>3.130000114440918</v>
+        <v>7.630000114440918</v>
       </c>
       <c r="E2" t="n">
-        <v>0.167560247813954</v>
+        <v>0.2614862166699909</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6177319884300232</v>
+        <v>0.6601638793945312</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5873745679855347</v>
+        <v>0.6190871596336365</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5828819274902344</v>
+        <v>0.6193735599517822</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5750670433044434</v>
+        <v>0.6068447232246399</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0732024237513542</v>
+        <v>0.1092932373285293</v>
       </c>
       <c r="K2" t="n">
-        <v>86.93393564224243</v>
+        <v>168.779278755188</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0629303614298502</v>
+        <v>0.06975041389465329</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0696653334299723</v>
+        <v>0.1192476479212443</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0598720995585123</v>
+        <v>0.09680219968159989</v>
       </c>
       <c r="O2" t="n">
-        <v>9.439554214477541</v>
+        <v>10.462562084198</v>
       </c>
       <c r="P2" t="n">
-        <v>10.44980001449585</v>
+        <v>17.88714718818665</v>
       </c>
       <c r="Q2" t="n">
-        <v>8.980814933776855</v>
+        <v>14.52032995223999</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250630-203740</t>
+          <t>20250729-142832</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -6052,7 +6052,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>rtdetr_18</t>
+          <t>rtdetr_50</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -6067,22 +6067,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -6114,56 +6114,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C3" t="n">
-        <v>274.2344217300415</v>
+        <v>599.8598256111145</v>
       </c>
       <c r="D3" t="n">
-        <v>3.259999990463257</v>
+        <v>7.96999979019165</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1634544702246785</v>
+        <v>0.2599702286720275</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6174442172050476</v>
+        <v>0.6633273959159851</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5955296158790588</v>
+        <v>0.6448784470558167</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5860681533813477</v>
+        <v>0.6398852467536926</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5697823166847229</v>
+        <v>0.6321436166763306</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0706546753644943</v>
+        <v>0.111848346889019</v>
       </c>
       <c r="K3" t="n">
-        <v>87.44894528388977</v>
+        <v>165.5598654747009</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0612700653076171</v>
+        <v>0.0694727977116902</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0706832345326741</v>
+        <v>0.1196835438410441</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0596227502822876</v>
+        <v>0.09185090859731029</v>
       </c>
       <c r="O3" t="n">
-        <v>9.190509796142578</v>
+        <v>10.42091965675354</v>
       </c>
       <c r="P3" t="n">
-        <v>10.60248517990112</v>
+        <v>17.95253157615662</v>
       </c>
       <c r="Q3" t="n">
-        <v>8.94341254234314</v>
+        <v>13.77763628959656</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250630-204506</t>
+          <t>20250729-144120</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -6173,7 +6173,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>rtdetr_18</t>
+          <t>rtdetr_50</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -6188,22 +6188,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -6235,56 +6235,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C4" t="n">
-        <v>273.5970973968506</v>
+        <v>606.978707075119</v>
       </c>
       <c r="D4" t="n">
-        <v>3.380000114440918</v>
+        <v>8.600000381469727</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1656858818605541</v>
+        <v>0.2618415892124176</v>
       </c>
       <c r="F4" t="n">
-        <v>0.604037880897522</v>
+        <v>0.6625048518180847</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5855168104171753</v>
+        <v>0.6393769979476929</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5803258419036865</v>
+        <v>0.6359631419181824</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5744157433509827</v>
+        <v>0.6225760579109192</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0719242990016937</v>
+        <v>0.1097427979111671</v>
       </c>
       <c r="K4" t="n">
-        <v>87.41053414344788</v>
+        <v>170.1154606342316</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0604438050587972</v>
+        <v>0.0695254977544148</v>
       </c>
       <c r="M4" t="n">
-        <v>0.07001307646433511</v>
+        <v>0.118765853246053</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0572473208109537</v>
+        <v>0.0943031597137451</v>
       </c>
       <c r="O4" t="n">
-        <v>9.06657075881958</v>
+        <v>10.42882466316223</v>
       </c>
       <c r="P4" t="n">
-        <v>10.50196146965027</v>
+        <v>17.81487798690796</v>
       </c>
       <c r="Q4" t="n">
-        <v>8.587098121643066</v>
+        <v>14.14547395706177</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250630-205213</t>
+          <t>20250729-145532</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -6294,7 +6294,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>rtdetr_18</t>
+          <t>rtdetr_50</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -6309,22 +6309,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -6359,53 +6359,53 @@
         <v>16</v>
       </c>
       <c r="C5" t="n">
-        <v>277.7233979701996</v>
+        <v>392.0192928314209</v>
       </c>
       <c r="D5" t="n">
-        <v>3.299999952316284</v>
+        <v>8.050000190734863</v>
       </c>
       <c r="E5" t="n">
-        <v>0.16512509342283</v>
+        <v>0.2609286271035671</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5899450182914734</v>
+        <v>0.6568144559860229</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5673962235450745</v>
+        <v>0.6195651888847351</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5643118023872375</v>
+        <v>0.6130653023719788</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5507428050041199</v>
+        <v>0.6030782461166382</v>
       </c>
       <c r="J5" t="n">
-        <v>0.07008471339941021</v>
+        <v>0.109289713203907</v>
       </c>
       <c r="K5" t="n">
-        <v>86.325923204422</v>
+        <v>168.6243941783905</v>
       </c>
       <c r="L5" t="n">
-        <v>0.062462051709493</v>
+        <v>0.0671900494893392</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0659398746490478</v>
+        <v>0.1154945421218872</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0584935617446899</v>
+        <v>0.09353352864583329</v>
       </c>
       <c r="O5" t="n">
-        <v>9.36930775642395</v>
+        <v>10.07850742340088</v>
       </c>
       <c r="P5" t="n">
-        <v>9.890981197357178</v>
+        <v>17.32418131828308</v>
       </c>
       <c r="Q5" t="n">
-        <v>8.774034261703491</v>
+        <v>14.030029296875</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250630-205929</t>
+          <t>20250729-150955</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -6415,7 +6415,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>rtdetr_18</t>
+          <t>rtdetr_50</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -6430,22 +6430,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -6477,56 +6477,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="C6" t="n">
-        <v>284.0024580955505</v>
+        <v>1211.803745985031</v>
       </c>
       <c r="D6" t="n">
-        <v>3.390000104904175</v>
+        <v>8.310000419616699</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1692056106403469</v>
+        <v>0.2603196914379413</v>
       </c>
       <c r="F6" t="n">
-        <v>0.61426842212677</v>
+        <v>0.6614481210708618</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5808395147323608</v>
+        <v>0.6502677798271179</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5760208368301392</v>
+        <v>0.6460340023040771</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5624184608459473</v>
+        <v>0.6420525908470154</v>
       </c>
       <c r="J6" t="n">
-        <v>0.06837094575166699</v>
+        <v>0.1091789752244949</v>
       </c>
       <c r="K6" t="n">
-        <v>103.2605590820312</v>
+        <v>165.9676139354706</v>
       </c>
       <c r="L6" t="n">
-        <v>0.064762684504191</v>
+        <v>0.0687694899241129</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0748015133539835</v>
+        <v>0.1183727741241455</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0618381516138712</v>
+        <v>0.0962396113077799</v>
       </c>
       <c r="O6" t="n">
-        <v>9.714402675628662</v>
+        <v>10.31542348861694</v>
       </c>
       <c r="P6" t="n">
-        <v>11.22022700309753</v>
+        <v>17.75591611862183</v>
       </c>
       <c r="Q6" t="n">
-        <v>9.275722742080688</v>
+        <v>14.43594169616699</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250630-210657</t>
+          <t>20250729-152052</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -6536,7 +6536,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>rtdetr_18</t>
+          <t>rtdetr_50</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -6551,22 +6551,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -6764,56 +6764,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C2" t="n">
-        <v>503.2358484268189</v>
+        <v>361.552216053009</v>
       </c>
       <c r="D2" t="n">
-        <v>6.980000019073486</v>
+        <v>10.6899995803833</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2567737670171828</v>
+        <v>0.1962353576247284</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6378539204597473</v>
+        <v>0.4076923131942749</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6128461956977844</v>
+        <v>0.3753877878189087</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6088253855705261</v>
+        <v>0.3744939267635345</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6040499806404114</v>
+        <v>0.378947377204895</v>
       </c>
       <c r="J2" t="n">
-        <v>0.09337889403104779</v>
+        <v>0.08116068691015239</v>
       </c>
       <c r="K2" t="n">
-        <v>167.1737134456635</v>
+        <v>61.5889093875885</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0706871652603149</v>
+        <v>0.0479188187917073</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1202723328272501</v>
+        <v>0.0414560222625732</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0948562939961751</v>
+        <v>0.0371037991841634</v>
       </c>
       <c r="O2" t="n">
-        <v>10.60307478904724</v>
+        <v>7.187822818756104</v>
       </c>
       <c r="P2" t="n">
-        <v>18.04084992408752</v>
+        <v>6.218403339385986</v>
       </c>
       <c r="Q2" t="n">
-        <v>14.22844409942627</v>
+        <v>5.565569877624512</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250701-093617</t>
+          <t>20250730-125915</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -6823,7 +6823,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>rtdetr_50</t>
+          <t>ssd_mobilenetv2</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -6838,22 +6838,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -6885,56 +6885,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="C3" t="n">
-        <v>412.3230001926422</v>
+        <v>291.5344371795654</v>
       </c>
       <c r="D3" t="n">
-        <v>7.019999980926514</v>
+        <v>10.63000011444092</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2547706181512159</v>
+        <v>0.1961856827591404</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6538158655166626</v>
+        <v>0.4150943458080292</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6227120757102966</v>
+        <v>0.3819047510623932</v>
       </c>
       <c r="H3" t="n">
-        <v>0.618996798992157</v>
+        <v>0.37561696767807</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6216673851013184</v>
+        <v>0.3778732120990753</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0965692102909088</v>
+        <v>0.0834553763270378</v>
       </c>
       <c r="K3" t="n">
-        <v>169.5687837600708</v>
+        <v>63.62542629241944</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07065320014953611</v>
+        <v>0.0446256526311238</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1196900049845377</v>
+        <v>0.0408802556991577</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0958293151855468</v>
+        <v>0.0376120503743489</v>
       </c>
       <c r="O3" t="n">
-        <v>10.59798002243042</v>
+        <v>6.693847894668579</v>
       </c>
       <c r="P3" t="n">
-        <v>17.95350074768066</v>
+        <v>6.132038354873657</v>
       </c>
       <c r="Q3" t="n">
-        <v>14.37439727783203</v>
+        <v>5.641807556152344</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250701-094855</t>
+          <t>20250730-130723</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>rtdetr_50</t>
+          <t>ssd_mobilenetv2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -6959,22 +6959,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -7006,56 +7006,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C4" t="n">
-        <v>588.5486900806427</v>
+        <v>239.4989309310913</v>
       </c>
       <c r="D4" t="n">
-        <v>7.659999847412109</v>
+        <v>10.69999980926514</v>
       </c>
       <c r="E4" t="n">
-        <v>0.255995317697525</v>
+        <v>0.1951687347005914</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6618098020553589</v>
+        <v>0.4210526347160339</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6141956448554993</v>
+        <v>0.3446745574474334</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6093546748161316</v>
+        <v>0.3445212244987488</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6044425368309021</v>
+        <v>0.340943694114685</v>
       </c>
       <c r="J4" t="n">
-        <v>0.08960806578397749</v>
+        <v>0.0905613675713539</v>
       </c>
       <c r="K4" t="n">
-        <v>169.1794247627258</v>
+        <v>61.94038200378418</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0661191511154174</v>
+        <v>0.0490723975499471</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1194165722529093</v>
+        <v>0.0416158167521158</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0932179530461629</v>
+        <v>0.037661805152893</v>
       </c>
       <c r="O4" t="n">
-        <v>9.917872667312622</v>
+        <v>7.360859632492065</v>
       </c>
       <c r="P4" t="n">
-        <v>17.9124858379364</v>
+        <v>6.242372512817383</v>
       </c>
       <c r="Q4" t="n">
-        <v>13.98269295692444</v>
+        <v>5.64927077293396</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250701-100006</t>
+          <t>20250730-131414</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -7065,7 +7065,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>rtdetr_50</t>
+          <t>ssd_mobilenetv2</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -7080,22 +7080,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -7127,56 +7127,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="C5" t="n">
-        <v>392.7058560848236</v>
+        <v>459.5452897548676</v>
       </c>
       <c r="D5" t="n">
-        <v>6.880000114440918</v>
+        <v>10.63000011444092</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2576020024716854</v>
+        <v>0.2031856956435185</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6561264991760254</v>
+        <v>0.4204444587230682</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6369105577468872</v>
+        <v>0.3882896900177002</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6385203003883362</v>
+        <v>0.385405957698822</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6264010071754456</v>
+        <v>0.3903441131114959</v>
       </c>
       <c r="J5" t="n">
-        <v>0.08969177305698391</v>
+        <v>0.09213345497846601</v>
       </c>
       <c r="K5" t="n">
-        <v>167.3052749633789</v>
+        <v>72.93836236000061</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0677739524841308</v>
+        <v>0.0459856176376342</v>
       </c>
       <c r="M5" t="n">
-        <v>0.117811902364095</v>
+        <v>0.0442177613576253</v>
       </c>
       <c r="N5" t="n">
-        <v>0.09401273250579829</v>
+        <v>0.0380756839116414</v>
       </c>
       <c r="O5" t="n">
-        <v>10.16609287261963</v>
+        <v>6.897842645645142</v>
       </c>
       <c r="P5" t="n">
-        <v>17.67178535461426</v>
+        <v>6.632664203643799</v>
       </c>
       <c r="Q5" t="n">
-        <v>14.10190987586975</v>
+        <v>5.711352586746216</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250701-101410</t>
+          <t>20250730-132010</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -7186,7 +7186,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>rtdetr_50</t>
+          <t>ssd_mobilenetv2</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -7201,22 +7201,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -7248,56 +7248,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19</v>
+        <v>81</v>
       </c>
       <c r="C6" t="n">
-        <v>460.8189880847931</v>
+        <v>691.8972628116608</v>
       </c>
       <c r="D6" t="n">
-        <v>7.130000114440918</v>
+        <v>10.69999980926514</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2570982293078774</v>
+        <v>0.1943213779617238</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6541910171508789</v>
+        <v>0.4320137798786163</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6424697637557983</v>
+        <v>0.3883403837680816</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6400166749954224</v>
+        <v>0.3890849351882934</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6256495714187622</v>
+        <v>0.3869299590587616</v>
       </c>
       <c r="J6" t="n">
-        <v>0.09973637759685509</v>
+        <v>0.087934099137783</v>
       </c>
       <c r="K6" t="n">
-        <v>171.7316739559174</v>
+        <v>62.29300713539124</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0661661593119303</v>
+        <v>0.0448477888107299</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1200235907236735</v>
+        <v>0.045197475751241</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0927974780400594</v>
+        <v>0.0345045073827107</v>
       </c>
       <c r="O6" t="n">
-        <v>9.924923896789551</v>
+        <v>6.727168321609497</v>
       </c>
       <c r="P6" t="n">
-        <v>18.00353860855103</v>
+        <v>6.779621362686157</v>
       </c>
       <c r="Q6" t="n">
-        <v>13.91962170600891</v>
+        <v>5.175676107406616</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250701-102508</t>
+          <t>20250730-132948</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -7307,7 +7307,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>rtdetr_50</t>
+          <t>ssd_mobilenetv2</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -7322,22 +7322,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -7535,56 +7535,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="C2" t="n">
-        <v>440.2437393665314</v>
+        <v>367.0427229404449</v>
       </c>
       <c r="D2" t="n">
-        <v>1.860000014305115</v>
+        <v>13.65999984741211</v>
       </c>
       <c r="E2" t="n">
-        <v>0.18740358441434</v>
+        <v>0.312769531176008</v>
       </c>
       <c r="F2" t="n">
-        <v>0.526147723197937</v>
+        <v>0.611237645149231</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4685687720775604</v>
+        <v>0.5820568799972534</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4659879803657532</v>
+        <v>0.5797101259231567</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4556902945041656</v>
+        <v>0.5777496695518494</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1455440521240234</v>
+        <v>0.0948221310973167</v>
       </c>
       <c r="K2" t="n">
-        <v>37.7447075843811</v>
+        <v>121.70130443573</v>
       </c>
       <c r="L2" t="n">
-        <v>0.068393219312032</v>
+        <v>0.0382272879282633</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0426359176635742</v>
+        <v>0.1141826025644938</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0448684008916219</v>
+        <v>0.0637834119796753</v>
       </c>
       <c r="O2" t="n">
-        <v>10.25898289680481</v>
+        <v>5.734093189239502</v>
       </c>
       <c r="P2" t="n">
-        <v>6.395387649536133</v>
+        <v>17.12739038467407</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.730260133743286</v>
+        <v>9.567511796951294</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250701-205539</t>
+          <t>20250731-043638</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -7594,7 +7594,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>rtmdet_tiny</t>
+          <t>yolox_l</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -7609,22 +7609,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -7656,56 +7656,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C3" t="n">
-        <v>331.2781541347504</v>
+        <v>517.0478546619415</v>
       </c>
       <c r="D3" t="n">
-        <v>1.860000014305115</v>
+        <v>13.65999984741211</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1865811743906565</v>
+        <v>0.3130681645579454</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5314912796020508</v>
+        <v>0.6250962018966675</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4759963750839233</v>
+        <v>0.5814053416252136</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4845894277095794</v>
+        <v>0.5850844383239746</v>
       </c>
       <c r="I3" t="n">
-        <v>0.473637580871582</v>
+        <v>0.574994683265686</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1472506523132324</v>
+        <v>0.0959547460079193</v>
       </c>
       <c r="K3" t="n">
-        <v>38.29838919639587</v>
+        <v>114.0442698001862</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06570157845815019</v>
+        <v>0.0408528200785319</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0382486867904663</v>
+        <v>0.115412704149882</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0402282683054606</v>
+        <v>0.0644522666931152</v>
       </c>
       <c r="O3" t="n">
-        <v>9.855236768722534</v>
+        <v>6.127923011779785</v>
       </c>
       <c r="P3" t="n">
-        <v>5.737303018569946</v>
+        <v>17.3119056224823</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.034240245819092</v>
+        <v>9.667840003967283</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250701-210427</t>
+          <t>20250731-044552</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -7715,7 +7715,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>rtmdet_tiny</t>
+          <t>yolox_l</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -7730,22 +7730,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -7777,56 +7777,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C4" t="n">
-        <v>498.5394446849823</v>
+        <v>610.2681579589844</v>
       </c>
       <c r="D4" t="n">
-        <v>1.840000033378601</v>
+        <v>13.65999984741211</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1888321534080324</v>
+        <v>0.3126465982320357</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5295424461364746</v>
+        <v>0.6369781494140625</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4705611765384674</v>
+        <v>0.593723475933075</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4645814299583435</v>
+        <v>0.5867302417755127</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4576693177223205</v>
+        <v>0.5807433128356934</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1722515225410461</v>
+        <v>0.09462460875511169</v>
       </c>
       <c r="K4" t="n">
-        <v>38.55291152000427</v>
+        <v>115.3599627017975</v>
       </c>
       <c r="L4" t="n">
-        <v>0.06802862644195549</v>
+        <v>0.040013190905253</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0406938107808431</v>
+        <v>0.1182834641138712</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0410377995173136</v>
+        <v>0.0636721436182657</v>
       </c>
       <c r="O4" t="n">
-        <v>10.20429396629334</v>
+        <v>6.001978635787964</v>
       </c>
       <c r="P4" t="n">
-        <v>6.104071617126465</v>
+        <v>17.74251961708069</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.155669927597046</v>
+        <v>9.550821542739868</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250701-211147</t>
+          <t>20250731-045730</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -7836,7 +7836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>rtmdet_tiny</t>
+          <t>yolox_l</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -7851,22 +7851,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -7898,56 +7898,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="C5" t="n">
-        <v>547.5143558979034</v>
+        <v>465.3066518306732</v>
       </c>
       <c r="D5" t="n">
-        <v>1.879999995231628</v>
+        <v>13.80000019073486</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1857515394182528</v>
+        <v>0.3106324455222568</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5266666412353516</v>
+        <v>0.6302124261856079</v>
       </c>
       <c r="G5" t="n">
-        <v>0.482619434595108</v>
+        <v>0.5848315954208374</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4821109175682068</v>
+        <v>0.5823771357536316</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4788205027580261</v>
+        <v>0.5807972550392151</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1482394933700561</v>
+        <v>0.0904812738299369</v>
       </c>
       <c r="K5" t="n">
-        <v>39.20951509475708</v>
+        <v>113.6001899242401</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0675631157557169</v>
+        <v>0.0379832029342651</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0395106363296508</v>
+        <v>0.1122475131352742</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0388945357004801</v>
+        <v>0.062924690246582</v>
       </c>
       <c r="O5" t="n">
-        <v>10.13446736335754</v>
+        <v>5.697480440139771</v>
       </c>
       <c r="P5" t="n">
-        <v>5.926595449447632</v>
+        <v>16.83712697029114</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.834180355072021</v>
+        <v>9.438703536987305</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250701-212154</t>
+          <t>20250731-051054</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -7957,7 +7957,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>rtmdet_tiny</t>
+          <t>yolox_l</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -7972,22 +7972,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -8019,56 +8019,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>87</v>
+        <v>21</v>
       </c>
       <c r="C6" t="n">
-        <v>805.3704330921173</v>
+        <v>270.3761479854584</v>
       </c>
       <c r="D6" t="n">
-        <v>1.870000004768372</v>
+        <v>13.64000034332275</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1867473855100828</v>
+        <v>0.3136637792700812</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5509594678878784</v>
+        <v>0.6064951419830322</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4897237420082092</v>
+        <v>0.552493155002594</v>
       </c>
       <c r="H6" t="n">
-        <v>0.491894394159317</v>
+        <v>0.5485541820526123</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4830222725868225</v>
+        <v>0.5406222939491272</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1507457494735717</v>
+        <v>0.0925003066658973</v>
       </c>
       <c r="K6" t="n">
-        <v>38.74946689605713</v>
+        <v>117.0328590869904</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0656683270136515</v>
+        <v>0.0368843571345011</v>
       </c>
       <c r="M6" t="n">
-        <v>0.038239296277364</v>
+        <v>0.1121730295817057</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0404864899317423</v>
+        <v>0.0624034547805786</v>
       </c>
       <c r="O6" t="n">
-        <v>9.850249052047729</v>
+        <v>5.532653570175171</v>
       </c>
       <c r="P6" t="n">
-        <v>5.735894441604614</v>
+        <v>16.82595443725586</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.072973489761353</v>
+        <v>9.360518217086792</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250701-213250</t>
+          <t>20250731-052150</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -8078,7 +8078,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>rtmdet_tiny</t>
+          <t>yolox_l</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -8093,22 +8093,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -8306,56 +8306,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="C2" t="n">
-        <v>216.8048763275146</v>
+        <v>448.6250975131989</v>
       </c>
       <c r="D2" t="n">
-        <v>5.590000152587891</v>
+        <v>6.96999979019165</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1873670828342437</v>
+        <v>0.1936255525458942</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4233576655387878</v>
+        <v>0.5659946799278259</v>
       </c>
       <c r="G2" t="n">
-        <v>0.351703405380249</v>
+        <v>0.5367303490638733</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3513784408569336</v>
+        <v>0.5369458198547363</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3541823625564575</v>
+        <v>0.5387062430381775</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0782732591032981</v>
+        <v>0.101590871810913</v>
       </c>
       <c r="K2" t="n">
-        <v>64.3450939655304</v>
+        <v>81.03700661659241</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0467229604721069</v>
+        <v>0.0413314421971639</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0449820836385091</v>
+        <v>0.0576924975713094</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0352388572692871</v>
+        <v>0.055047378540039</v>
       </c>
       <c r="O2" t="n">
-        <v>7.00844407081604</v>
+        <v>6.199716329574585</v>
       </c>
       <c r="P2" t="n">
-        <v>6.747312545776367</v>
+        <v>8.653874635696411</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.285828590393066</v>
+        <v>8.257106781005859</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250702-121632</t>
+          <t>20250627-172835</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -8365,7 +8365,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>ssd_mobilenetv2</t>
+          <t>atss_mobilenetv2</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -8430,53 +8430,53 @@
         <v>41</v>
       </c>
       <c r="C3" t="n">
-        <v>343.9584999084473</v>
+        <v>338.2517077922821</v>
       </c>
       <c r="D3" t="n">
-        <v>5.599999904632568</v>
+        <v>6.71999979019165</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1852508888738911</v>
+        <v>0.1935463482286871</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4290780127048492</v>
+        <v>0.5704028606414795</v>
       </c>
       <c r="G3" t="n">
-        <v>0.388930082321167</v>
+        <v>0.5346410870552063</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3907251954078674</v>
+        <v>0.5355722308158875</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3896551728248596</v>
+        <v>0.5385469794273376</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0789182186126709</v>
+        <v>0.1004696562886238</v>
       </c>
       <c r="K3" t="n">
-        <v>64.07507681846619</v>
+        <v>79.39242696762085</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0448702828089396</v>
+        <v>0.0392441908518473</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0425754324595133</v>
+        <v>0.0540985774993896</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0382912683486938</v>
+        <v>0.054418404897054</v>
       </c>
       <c r="O3" t="n">
-        <v>6.730542421340942</v>
+        <v>5.8866286277771</v>
       </c>
       <c r="P3" t="n">
-        <v>6.386314868927002</v>
+        <v>8.114786624908447</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.743690252304077</v>
+        <v>8.162760734558105</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250702-122209</t>
+          <t>20250627-173818</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -8486,7 +8486,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>ssd_mobilenetv2</t>
+          <t>atss_mobilenetv2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -8548,56 +8548,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C4" t="n">
-        <v>232.2008743286133</v>
+        <v>211.3316407203674</v>
       </c>
       <c r="D4" t="n">
-        <v>5.599999904632568</v>
+        <v>6.710000038146973</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1879238635301589</v>
+        <v>0.1946363520622253</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4114088118076324</v>
+        <v>0.5670216679573059</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3491902947425842</v>
+        <v>0.536729097366333</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3498771488666534</v>
+        <v>0.5373949408531189</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3493427634239197</v>
+        <v>0.5356004238128662</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0806476920843124</v>
+        <v>0.0968440026044845</v>
       </c>
       <c r="K4" t="n">
-        <v>62.67044544219971</v>
+        <v>81.23124194145203</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0465223439534505</v>
+        <v>0.0387825568517049</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0423571729660034</v>
+        <v>0.055232655207316</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0394002389907836</v>
+        <v>0.0552035125096639</v>
       </c>
       <c r="O4" t="n">
-        <v>6.978351593017578</v>
+        <v>5.817383527755737</v>
       </c>
       <c r="P4" t="n">
-        <v>6.353575944900513</v>
+        <v>8.284898281097412</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.910035848617554</v>
+        <v>8.280526876449585</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250702-122953</t>
+          <t>20250627-174620</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -8607,7 +8607,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>ssd_mobilenetv2</t>
+          <t>atss_mobilenetv2</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -8669,56 +8669,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="C5" t="n">
-        <v>403.6053516864777</v>
+        <v>273.1337945461273</v>
       </c>
       <c r="D5" t="n">
-        <v>5.590000152587891</v>
+        <v>6.71999979019165</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1928627513190532</v>
+        <v>0.1931538392197001</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4325657784938812</v>
+        <v>0.5707565546035767</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3919982016086578</v>
+        <v>0.5261584520339966</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3930917084217071</v>
+        <v>0.5249679684638977</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3908312022686004</v>
+        <v>0.5229259729385376</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0844565480947494</v>
+        <v>0.0980679020285606</v>
       </c>
       <c r="K5" t="n">
-        <v>62.43181729316712</v>
+        <v>79.88996696472168</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0459198029836018</v>
+        <v>0.0382463757197062</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0466434987386067</v>
+        <v>0.0542384513219197</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0356898419062296</v>
+        <v>0.0522336626052856</v>
       </c>
       <c r="O5" t="n">
-        <v>6.887970447540283</v>
+        <v>5.736956357955933</v>
       </c>
       <c r="P5" t="n">
-        <v>6.996524810791016</v>
+        <v>8.135767698287964</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.353476285934448</v>
+        <v>7.835049390792847</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250702-123544</t>
+          <t>20250627-175217</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -8728,7 +8728,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>ssd_mobilenetv2</t>
+          <t>atss_mobilenetv2</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -8790,56 +8790,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C6" t="n">
-        <v>355.0107519626617</v>
+        <v>289.305410861969</v>
       </c>
       <c r="D6" t="n">
-        <v>5.659999847412109</v>
+        <v>6.96999979019165</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1931373102635871</v>
+        <v>0.1930527384792054</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4239130318164825</v>
+        <v>0.5642105340957642</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3911958336830139</v>
+        <v>0.5289501547813416</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3908098340034485</v>
+        <v>0.5277777910232544</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3868181705474853</v>
+        <v>0.5268358588218689</v>
       </c>
       <c r="J6" t="n">
-        <v>0.085229717195034</v>
+        <v>0.0949276313185691</v>
       </c>
       <c r="K6" t="n">
-        <v>64.09615087509155</v>
+        <v>80.33323335647583</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0459905306498209</v>
+        <v>0.0387941757837931</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0420664850870768</v>
+        <v>0.0570641485850016</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0388242149353027</v>
+        <v>0.0534342877070109</v>
       </c>
       <c r="O6" t="n">
-        <v>6.898579597473145</v>
+        <v>5.81912636756897</v>
       </c>
       <c r="P6" t="n">
-        <v>6.309972763061523</v>
+        <v>8.559622287750244</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.82363224029541</v>
+        <v>8.015143156051636</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250702-124425</t>
+          <t>20250627-175913</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -8849,7 +8849,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>ssd_mobilenetv2</t>
+          <t>atss_mobilenetv2</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -9077,56 +9077,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C2" t="n">
-        <v>436.8241927623749</v>
+        <v>440.2437393665314</v>
       </c>
       <c r="D2" t="n">
-        <v>7.480000019073486</v>
+        <v>1.860000014305115</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2338451587183531</v>
+        <v>0.18740358441434</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6236132979393005</v>
+        <v>0.526147723197937</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5763527154922485</v>
+        <v>0.4685687720775604</v>
       </c>
       <c r="H2" t="n">
-        <v>0.569509744644165</v>
+        <v>0.4659879803657532</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5571331977844238</v>
+        <v>0.4556902945041656</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0994065105915069</v>
+        <v>0.1455440521240234</v>
       </c>
       <c r="K2" t="n">
-        <v>112.455070734024</v>
+        <v>37.7447075843811</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0454493729273478</v>
+        <v>0.068393219312032</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1152875248591105</v>
+        <v>0.0426359176635742</v>
       </c>
       <c r="N2" t="n">
-        <v>0.060280164082845</v>
+        <v>0.0448684008916219</v>
       </c>
       <c r="O2" t="n">
-        <v>6.817405939102173</v>
+        <v>10.25898289680481</v>
       </c>
       <c r="P2" t="n">
-        <v>17.29312872886658</v>
+        <v>6.395387649536133</v>
       </c>
       <c r="Q2" t="n">
-        <v>9.042024612426758</v>
+        <v>6.730260133743286</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250703-130520</t>
+          <t>20250701-205539</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>yolox_l</t>
+          <t>rtmdet_tiny</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -9198,56 +9198,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C3" t="n">
-        <v>412.3185155391693</v>
+        <v>331.2781541347504</v>
       </c>
       <c r="D3" t="n">
-        <v>7.570000171661377</v>
+        <v>1.860000014305115</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2312289705363715</v>
+        <v>0.1865811743906565</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6273764371871948</v>
+        <v>0.5314912796020508</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5815891027450562</v>
+        <v>0.4759963750839233</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5826873183250427</v>
+        <v>0.4845894277095794</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5750528573989868</v>
+        <v>0.473637580871582</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0764109641313552</v>
+        <v>0.1472506523132324</v>
       </c>
       <c r="K3" t="n">
-        <v>112.6497087478638</v>
+        <v>38.29838919639587</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0455627552668253</v>
+        <v>0.06570157845815019</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1170696640014648</v>
+        <v>0.0382486867904663</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0637941551208496</v>
+        <v>0.0402282683054606</v>
       </c>
       <c r="O3" t="n">
-        <v>6.834413290023804</v>
+        <v>9.855236768722534</v>
       </c>
       <c r="P3" t="n">
-        <v>17.56044960021973</v>
+        <v>5.737303018569946</v>
       </c>
       <c r="Q3" t="n">
-        <v>9.56912326812744</v>
+        <v>6.034240245819092</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250703-131549</t>
+          <t>20250701-210427</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>yolox_l</t>
+          <t>rtmdet_tiny</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -9319,56 +9319,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C4" t="n">
-        <v>486.4648160934448</v>
+        <v>498.5394446849823</v>
       </c>
       <c r="D4" t="n">
-        <v>7.630000114440918</v>
+        <v>1.840000033378601</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2330227229668169</v>
+        <v>0.1888321534080324</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6358100175857544</v>
+        <v>0.5295424461364746</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6021413207054138</v>
+        <v>0.4705611765384674</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5956732034683228</v>
+        <v>0.4645814299583435</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5854998826980591</v>
+        <v>0.4576693177223205</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0751330628991127</v>
+        <v>0.1722515225410461</v>
       </c>
       <c r="K4" t="n">
-        <v>114.7178599834442</v>
+        <v>38.55291152000427</v>
       </c>
       <c r="L4" t="n">
-        <v>0.044731806119283</v>
+        <v>0.06802862644195549</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1171044953664143</v>
+        <v>0.0406938107808431</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0644216966629028</v>
+        <v>0.0410377995173136</v>
       </c>
       <c r="O4" t="n">
-        <v>6.709770917892456</v>
+        <v>10.20429396629334</v>
       </c>
       <c r="P4" t="n">
-        <v>17.56567430496216</v>
+        <v>6.104071617126465</v>
       </c>
       <c r="Q4" t="n">
-        <v>9.663254499435425</v>
+        <v>6.155669927597046</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250703-132544</t>
+          <t>20250701-211147</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>yolox_l</t>
+          <t>rtmdet_tiny</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -9440,56 +9440,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="C5" t="n">
-        <v>395.9152064323425</v>
+        <v>547.5143558979034</v>
       </c>
       <c r="D5" t="n">
-        <v>7.53000020980835</v>
+        <v>1.879999995231628</v>
       </c>
       <c r="E5" t="n">
-        <v>0.233429567171977</v>
+        <v>0.1857515394182528</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6117556095123291</v>
+        <v>0.5266666412353516</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5513157844543457</v>
+        <v>0.482619434595108</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5545318126678467</v>
+        <v>0.4821109175682068</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5518582463264465</v>
+        <v>0.4788205027580261</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0785158053040504</v>
+        <v>0.1482394933700561</v>
       </c>
       <c r="K5" t="n">
-        <v>114.705659866333</v>
+        <v>39.20951509475708</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0454021883010864</v>
+        <v>0.0675631157557169</v>
       </c>
       <c r="M5" t="n">
-        <v>0.117553170522054</v>
+        <v>0.0395106363296508</v>
       </c>
       <c r="N5" t="n">
-        <v>0.061805419921875</v>
+        <v>0.0388945357004801</v>
       </c>
       <c r="O5" t="n">
-        <v>6.810328245162964</v>
+        <v>10.13446736335754</v>
       </c>
       <c r="P5" t="n">
-        <v>17.63297557830811</v>
+        <v>5.926595449447632</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.27081298828125</v>
+        <v>5.834180355072021</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250703-133654</t>
+          <t>20250701-212154</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -9499,7 +9499,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>yolox_l</t>
+          <t>rtmdet_tiny</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -9561,56 +9561,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33</v>
+        <v>87</v>
       </c>
       <c r="C6" t="n">
-        <v>335.4362275600433</v>
+        <v>805.3704330921173</v>
       </c>
       <c r="D6" t="n">
-        <v>7.5</v>
+        <v>1.870000004768372</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2325969830606922</v>
+        <v>0.1867473855100828</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6182669997215271</v>
+        <v>0.5509594678878784</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5869475603103638</v>
+        <v>0.4897237420082092</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5797356963157654</v>
+        <v>0.491894394159317</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5742793679237366</v>
+        <v>0.4830222725868225</v>
       </c>
       <c r="J6" t="n">
-        <v>0.100102461874485</v>
+        <v>0.1507457494735717</v>
       </c>
       <c r="K6" t="n">
-        <v>112.5011727809906</v>
+        <v>38.74946689605713</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0472533750534057</v>
+        <v>0.0656683270136515</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1164957888921102</v>
+        <v>0.038239296277364</v>
       </c>
       <c r="N6" t="n">
-        <v>0.06362141768137609</v>
+        <v>0.0404864899317423</v>
       </c>
       <c r="O6" t="n">
-        <v>7.088006258010864</v>
+        <v>9.850249052047729</v>
       </c>
       <c r="P6" t="n">
-        <v>17.47436833381653</v>
+        <v>5.735894441604614</v>
       </c>
       <c r="Q6" t="n">
-        <v>9.543212652206419</v>
+        <v>6.072973489761353</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250703-134645</t>
+          <t>20250701-213250</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -9620,7 +9620,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>yolox_l</t>
+          <t>rtmdet_tiny</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
